--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/IOWA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/IOWA_2010.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C99">
